--- a/dataset/construct/dataset_splits/data_size/20_percent/tum/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/tum/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2131</v>
+        <v>1550</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>91.6978407420083</v>
+        <v>84.8388366986083</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>30.4866850321395</v>
       </c>
       <c r="E2" t="n">
-        <v>24.0569347455645</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>110.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>297.5</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>575.2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1238.7</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>86.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>93.3</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>110.9</v>
+        <v>23</v>
       </c>
       <c r="V2" t="n">
-        <v>110.9</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>23.332060096766</v>
       </c>
       <c r="X2" t="n">
-        <v>24.9</v>
+        <v>22.7605444857119</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.246478873239437</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.7644512350395</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.2811760572589</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -728,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -737,22 +724,13 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
         <v>120</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>619</v>
+        <v>899</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -760,82 +738,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.8920669505919</v>
+        <v>80.2974793076787</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>27.7769298861451</v>
       </c>
       <c r="E3" t="n">
-        <v>24.8015873015873</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>407</v>
       </c>
       <c r="I3" t="n">
-        <v>498</v>
+        <v>208</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="K3" t="n">
-        <v>374</v>
+        <v>919</v>
       </c>
       <c r="L3" t="n">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="N3" t="n">
-        <v>739</v>
+        <v>155</v>
       </c>
       <c r="O3" t="n">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>8</v>
       </c>
-      <c r="R3" t="n">
-        <v>82</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X3" t="n">
-        <v>24.4</v>
+        <v>26.9117274486368</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.199261992619926</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.0509294626942</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.6608768976369</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -844,39 +822,30 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>693</v>
+        <v>364</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,79 +853,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.651817628717</v>
+        <v>83.7306500177453</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27.639801313892</v>
       </c>
       <c r="E4" t="n">
-        <v>19.6623076682999</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="I4" t="n">
-        <v>1330</v>
+        <v>72</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>709</v>
+        <v>289</v>
       </c>
       <c r="L4" t="n">
-        <v>417</v>
+        <v>116</v>
       </c>
       <c r="M4" t="n">
-        <v>447</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>193</v>
+        <v>21.15</v>
       </c>
       <c r="V4" t="n">
-        <v>242</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X4" t="n">
-        <v>25.1</v>
+        <v>20.8029488434442</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.304054054054054</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.7830404889228</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.8203626912254</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -974,31 +943,22 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>368</v>
+        <v>528</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1006,77 +966,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.1969855755824</v>
+        <v>84.2009601490608</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20.5498866213151</v>
       </c>
       <c r="E5" t="n">
-        <v>26.0261748958953</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>118.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>74.2</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1100</v>
+        <v>275</v>
       </c>
       <c r="L5" t="n">
-        <v>297</v>
+        <v>35.2</v>
       </c>
       <c r="M5" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1657</v>
+        <v>6.5</v>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
+        <v>41.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>60</v>
+        <v>13.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X5" t="n">
-        <v>22.35</v>
+        <v>22.0850401322991</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.226190476190476</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.3940969210825</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1091,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1103,24 +1065,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2308</v>
+        <v>1587</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1128,82 +1081,82 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76.85541314928891</v>
+        <v>83.3414449768043</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24.8970602317341</v>
       </c>
       <c r="E6" t="n">
-        <v>28.2828282828282</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>307.5</v>
       </c>
       <c r="I6" t="n">
-        <v>315</v>
+        <v>269.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>185.9</v>
       </c>
       <c r="K6" t="n">
-        <v>387.4</v>
+        <v>762.6</v>
       </c>
       <c r="L6" t="n">
-        <v>356.4</v>
+        <v>8.4</v>
       </c>
       <c r="M6" t="n">
-        <v>395.4</v>
+        <v>42.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1139.2</v>
+        <v>94.8</v>
       </c>
       <c r="O6" t="n">
-        <v>119.7</v>
+        <v>145.7</v>
       </c>
       <c r="P6" t="n">
-        <v>53.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>175.5</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>348.4</v>
+        <v>78.8</v>
       </c>
       <c r="S6" t="n">
-        <v>14.9</v>
+        <v>96.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>127.4</v>
+        <v>23.15</v>
       </c>
       <c r="V6" t="n">
-        <v>142.3</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X6" t="n">
-        <v>23.05</v>
+        <v>23.0936433298824</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.298892988929889</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.8545963840081</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.1741916431478</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1227,24 +1180,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>256</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1315</v>
+        <v>2413</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1252,85 +1196,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77.34847025756081</v>
+        <v>83.4834113494055</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>37.6542220797949</v>
       </c>
       <c r="E7" t="n">
-        <v>29.0687732977668</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>1003.9</v>
       </c>
       <c r="I7" t="n">
-        <v>933</v>
+        <v>83</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>22.2</v>
       </c>
       <c r="K7" t="n">
-        <v>645.9</v>
+        <v>1109.1</v>
       </c>
       <c r="L7" t="n">
-        <v>346.9</v>
+        <v>34.4</v>
       </c>
       <c r="M7" t="n">
-        <v>419.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1412.3</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="P7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>98.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V7" t="n">
-        <v>26</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.1729055258467</v>
       </c>
       <c r="X7" t="n">
-        <v>26.8</v>
+        <v>22.6034185328367</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.207357859531773</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>27.6292335115865</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>26.9920118011893</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1345,30 +1289,21 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2338</v>
+        <v>1720</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,121 +1311,114 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.2657497718458</v>
+        <v>68.3052995474941</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>30.7173999207292</v>
       </c>
       <c r="E8" t="n">
-        <v>25.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>166.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>262</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="K8" t="n">
-        <v>237.9</v>
+        <v>676.7</v>
       </c>
       <c r="L8" t="n">
-        <v>111.4</v>
+        <v>44.4</v>
       </c>
       <c r="M8" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>391.7</v>
+        <v>95.2</v>
       </c>
       <c r="O8" t="n">
-        <v>72.8</v>
+        <v>139.6</v>
       </c>
       <c r="P8" t="n">
-        <v>5.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>102.5</v>
+        <v>99.8</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>123.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>46.5</v>
+        <v>24.25</v>
       </c>
       <c r="V8" t="n">
-        <v>46.5</v>
+        <v>0.29</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X8" t="n">
-        <v>19.65</v>
+        <v>23.0936433298824</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.205479452054795</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.9261522790935</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.6934438757455</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>220</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>471</v>
+        <v>556</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1498,79 +1426,79 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75.0402101553984</v>
+        <v>78.32835766978479</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25.8264462809917</v>
       </c>
       <c r="E9" t="n">
-        <v>24.2105958514995</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
+        <v>855</v>
       </c>
       <c r="I9" t="n">
-        <v>200</v>
+        <v>523</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>457</v>
       </c>
       <c r="K9" t="n">
-        <v>464</v>
+        <v>1835</v>
       </c>
       <c r="L9" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1824</v>
+        <v>77</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>24.95</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X9" t="n">
-        <v>25.8</v>
+        <v>24.9992044677091</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.6557168321874</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>24.7175864208069</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1579,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1588,33 +1516,24 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,77 +1541,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85.91221886328491</v>
+        <v>82.3836315499278</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>29.585798816568</v>
       </c>
       <c r="E10" t="n">
-        <v>25.8805706350208</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>291</v>
+      </c>
+      <c r="I10" t="n">
+        <v>121</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="K10" t="n">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="L10" t="n">
-        <v>378</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1013</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>52</v>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>21.4</v>
       </c>
       <c r="V10" t="n">
-        <v>33</v>
+        <v>0.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>21.6450216450216</v>
       </c>
       <c r="X10" t="n">
-        <v>29.3</v>
+        <v>20.9857015385198</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.16875</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>28.9661319073084</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>28.6082260699118</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1719,24 +1640,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>254</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>657</v>
+        <v>914</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,82 +1656,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.0759392349228</v>
+        <v>84.0671732958146</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25.7629805786761</v>
       </c>
       <c r="E11" t="n">
-        <v>28.6501377410468</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>855</v>
+      </c>
+      <c r="I11" t="n">
+        <v>534</v>
+      </c>
+      <c r="J11" t="n">
+        <v>428</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1817</v>
+      </c>
+      <c r="L11" t="n">
         <v>50</v>
       </c>
-      <c r="I11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>819.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="M11" t="n">
-        <v>237.1</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
-        <v>1155.4</v>
+        <v>113</v>
       </c>
       <c r="O11" t="n">
-        <v>19.5</v>
+        <v>170</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>40.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>59.7</v>
+        <v>93</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>29.921059332824</v>
       </c>
       <c r="X11" t="n">
-        <v>21.85</v>
+        <v>29.2679951700071</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.357142857142857</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.3002291825821</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.1454723050462</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1828,33 +1740,24 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>200</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
